--- a/Excel/TSLX_Earnings.xlsx
+++ b/Excel/TSLX_Earnings.xlsx
@@ -413,41 +413,46 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Announced</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Period End</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EPS Actual</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>EPS Est</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Surprise %</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
@@ -461,22 +466,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>1Q26</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.42</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.49</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>-14.3</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>MISS</t>
         </is>
@@ -490,22 +500,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>4Q25</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>0.52</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.02</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>4</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -515,22 +530,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>3Q25</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>0.53</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.52</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.01</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1.9</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -540,22 +560,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>2Q25</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.53</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.03</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>5.7</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -565,22 +590,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>1Q25</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>0.58</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.02</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>3.6</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -590,22 +620,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>4Q24</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>0.61</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0.57</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.04</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -615,22 +650,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>3Q24</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>0.57</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0.58</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-1.7</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -640,22 +680,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>2Q24</t>
         </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.58</v>
       </c>
       <c r="D9" t="n">
         <v>0.58</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -665,22 +710,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>1Q24</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>0.58</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>0.59</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-1.7</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -690,22 +740,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>2023-12-31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>4Q23</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>0.62</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>0.58</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.04</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>6.9</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -715,22 +770,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>3Q23</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>0.6</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.03</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>5.3</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -740,22 +800,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>2Q23</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>0.59</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>0.55</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.04</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>7.3</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -765,22 +830,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>1Q23</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>0.55</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>0.54</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>0.01</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1.9</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -790,22 +860,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>4Q22</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>0.64</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>0.57</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>12.3</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -819,22 +894,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>3Q22</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>0.47</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>0.49</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>-4.1</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -844,22 +924,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>2022-06-30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>2Q22</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>0.51</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>0.48</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>0.03</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>6.3</v>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -869,22 +954,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>1Q22</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>0.49</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>0.5</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-2</v>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -894,22 +984,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>2021-12-31</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>4Q21</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>0.63</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>0.52</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.11</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>21.2</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -923,22 +1018,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>3Q21</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>0.55</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.05</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>10</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -952,22 +1052,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>2Q21</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>0.46</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>0.5</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-8</v>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -977,22 +1082,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>2021-03-31</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>1Q21</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>0.53</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>0.49</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.04</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1002,22 +1112,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>2020-12-31</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>4Q20</t>
         </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.5</v>
       </c>
       <c r="D23" t="n">
         <v>0.5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1027,22 +1142,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>2020-09-30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>3Q20</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>0.61</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>0.45</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>0.16</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>35.6</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1056,22 +1176,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>2020-06-30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>2Q20</t>
         </is>
-      </c>
-      <c r="C25" t="n">
-        <v>0.59</v>
       </c>
       <c r="D25" t="n">
         <v>0.59</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1081,22 +1206,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>1Q20</t>
         </is>
-      </c>
-      <c r="C26" t="n">
-        <v>0.51</v>
       </c>
       <c r="D26" t="n">
         <v>0.51</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1106,22 +1236,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>2019-12-31</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>4Q19</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>0.51</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>0.47</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>0.04</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>8.5</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1131,22 +1266,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>2019-09-30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>3Q19</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>0.55</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0.48</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>14.6</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1160,22 +1300,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>2019-06-30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>2Q19</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>0.47</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.46</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0.01</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>2.2</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1185,22 +1330,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>2019-03-31</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>1Q19</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>0.41</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>0.45</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>-8.9</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1210,22 +1360,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>2018-12-31</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t>4Q18</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>0.67</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>0.52</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>0.15</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>28.8</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1239,22 +1394,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>2018-09-30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>3Q18</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>0.5</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>0.49</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>0.01</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>2</v>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1264,22 +1424,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>2018-06-30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
           <t>2Q18</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>0.47</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>0.09</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>19.1</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1293,22 +1458,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
           <t>1Q18</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="D34" t="n">
         <v>0.51</v>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>0.46</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>0.05</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>10.9</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1322,22 +1492,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>2017-12-31</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>4Q17</t>
         </is>
-      </c>
-      <c r="C35" t="n">
-        <v>0.45</v>
       </c>
       <c r="D35" t="n">
         <v>0.45</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1347,22 +1522,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>3Q17</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>0.51</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>0.43</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>0.08</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>18.6</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1376,22 +1556,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>2017-06-30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>2Q17</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>0.57</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>0.46</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>0.11</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>23.9</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1405,22 +1590,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>2017-03-31</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>1Q17</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>0.48</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>0.44</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>0.04</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>9.1</v>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1430,22 +1620,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>2016-12-31</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>4Q16</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>0.47</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>0.44</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>0.03</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>6.8</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1455,22 +1650,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>2016-09-30</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>3Q16</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>0.51</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>0.44</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>15.9</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1484,22 +1684,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>2016-06-30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
           <t>2Q16</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>0.43</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>0.42</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>0.01</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>2.4</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1509,22 +1714,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>1Q16</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="D42" t="n">
         <v>0.42</v>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>0.43</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1534,22 +1744,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>2015-12-31</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>4Q15</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="D43" t="n">
         <v>0.44</v>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>0.43</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>0.01</v>
       </c>
-      <c r="F43" t="n">
+      <c r="G43" t="n">
         <v>2.3</v>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1559,22 +1774,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>2015-09-30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
           <t>3Q15</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="D44" t="n">
         <v>0.48</v>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>0.42</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>0.06</v>
       </c>
-      <c r="F44" t="n">
+      <c r="G44" t="n">
         <v>14.3</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1588,22 +1808,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>2015-06-30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
           <t>2Q15</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="D45" t="n">
         <v>0.46</v>
       </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
         <v>0.41</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>0.05</v>
       </c>
-      <c r="F45" t="n">
+      <c r="G45" t="n">
         <v>12.2</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1617,22 +1842,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>2015-03-31</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
           <t>1Q15</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="D46" t="n">
         <v>0.39</v>
       </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
         <v>0.41</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F46" t="n">
+      <c r="G46" t="n">
         <v>-4.9</v>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1642,22 +1872,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>2014-12-31</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
           <t>4Q14</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="D47" t="n">
         <v>0.57</v>
       </c>
-      <c r="D47" t="n">
+      <c r="E47" t="n">
         <v>0.4</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>0.17</v>
       </c>
-      <c r="F47" t="n">
+      <c r="G47" t="n">
         <v>42.5</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1671,22 +1906,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>2014-09-30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>3Q14</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>0.43</v>
       </c>
-      <c r="D48" t="n">
+      <c r="E48" t="n">
         <v>0.38</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>0.05</v>
       </c>
-      <c r="F48" t="n">
+      <c r="G48" t="n">
         <v>13.2</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1700,22 +1940,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>2014-06-30</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
           <t>2Q14</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="D49" t="n">
         <v>0.55</v>
       </c>
-      <c r="D49" t="n">
+      <c r="E49" t="n">
         <v>0.44</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>0.11</v>
       </c>
-      <c r="F49" t="n">
+      <c r="G49" t="n">
         <v>25</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
@@ -1729,22 +1974,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>2014-03-31</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>1Q14</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="D50" t="n">
         <v>0.51</v>
       </c>
-      <c r="D50" t="n">
+      <c r="E50" t="n">
         <v>0.41</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>0.1</v>
       </c>
-      <c r="F50" t="n">
+      <c r="G50" t="n">
         <v>24.4</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>BEAT</t>
         </is>
